--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -2546,7 +2546,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>c.1735</t>
+          <t>environ 1735</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>c.1671</t>
+          <t>environ 1671</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>c.1746</t>
+          <t>environ 1746</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -526,47 +526,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/28/Pompeo_Girolamo_Batoni_Thomas_William_Coke.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adélaïde</t>
+          <t>Pompeo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LABILLE-GUIARD</t>
+          <t>BATONI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Holkham Hall</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>"Autoportrait avec deux élèves"</t>
+          <t>"Portrait de Thomas William Coke"</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>"Ritratto di Thomas William Coke"</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -574,19 +579,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>210,8 cm</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>151,1 cm</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -596,57 +591,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/19/Labille-Guiard_Robespierre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/33/Pompeo_Batoni_002.jpg/960px-Pompeo_Batoni_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adélaïde</t>
+          <t>Pompeo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LABILLE-GUIARD</t>
+          <t>BATONI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Musée Carnavalet</t>
+          <t>Kunsthistorisches Museum</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>"Portrait de Robespierre"</t>
+          <t>"Portrait de Joseph II et Léopold de Toscane"</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>"Ritratto di Giuseppe II e Leopoldo di Toscana"</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c.246 cm</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>c.172 cm</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -656,52 +666,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg/960px-La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/02/Canaletto_-_Dresden_seen_from_the_Right_Bank_of_the_Elbe%2C_beneath_the_Augusts_Bridge_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ROSLIN</t>
+          <t>BELLOTTO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Dresde</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nationalmuseum</t>
+          <t>Gemäldegalerie</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>"La Dame au voile"</t>
+          <t>"Vue de Dresde depuis la rive droite de l'Elbe"</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>"Damen med slöjan"</t>
+          <t>"Dresda vista dalla riva destra dell'Elba"</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -709,19 +719,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>63 cm</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>52 cm</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>suédoise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -731,27 +731,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg/960px-Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Bellotto_View_of_Warsaw_from_Praga.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ROSLIN</t>
+          <t>BELLOTTO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -759,44 +759,29 @@
           <t>1770</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nationalmuseum</t>
+          <t>Musée national de Varsovie</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
+          <t>"Vue de Varsovie depuis Praga"</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>"Självporträtt"</t>
+          <t>"Veduta di Varsavia dalla Praga"</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pastel</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>46 cm</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>38 cm</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>suédoise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -806,57 +791,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Allan_Ramsay_%281713-84%29_-_George_III_%281738-1820%29_-_RCIN_405307_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ac/Europe_a_Prophecy_copy_K_plate_01.jpg/960px-Europe_a_Prophecy_copy_K_plate_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allan</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RAMSAY</t>
+          <t>BLAKE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>l’Université de Cambridge</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Royal Collection</t>
+          <t>Fitzwilliam Museum</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>"Portrait de George III"</t>
+          <t>"L’Ancien des Jours ou Le Grand Architecte"</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>"Portrait of George III"</t>
+          <t>"The Ancient of Days"</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Gravure à l'eau-forte rehaussée à l'aquarelle et à l'encre</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>23,3 cm</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>16,8 cm</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -871,52 +866,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Allan_Ramsay_-_Jean-Jacques_Rousseau_%281712_-_1778%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/ac/Catherine_II_walking_by_V.Borovikovskiy_%281794%2C_Tretyakov_gallery%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Allan</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAMSAY</t>
+          <t>BOROVIKOVSKY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Édimbourg</t>
+          <t>Moscou</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Scottish National Portrait Gallery</t>
+          <t>Galerie Tretiakov</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>"Portrait de Jean-Jacques Rousseau"</t>
+          <t>"Catherine II en promenade au parc de Tsarskoïe Selo"</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>"Portrait of Jean-Jacques Rousseau"</t>
+          <t>"Portret Yekateriny II na progulke (Портрет Екатерины II на прогулке)"</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -924,19 +919,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>75,9 cm</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>62,9 cm</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -946,52 +931,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Kauffmann_Cornelia_mater_Gracchorum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/70/Borovikovsky_pt_gagarinyh.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angelica</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KAUFFMAN</t>
+          <t>BOROVIKOVSKY</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Moscou</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Virginia Museum of Fine Arts</t>
+          <t>Galerie Tretiakov</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>"Cornelia, mère des Gracques"</t>
+          <t>"Portrait des sœurs Gagarine"</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>"Cornelia, Mother of the Gracchi"</t>
+          <t>"Portret sestyor Gagarinykh (Портрет сестёр Гагариных)"</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -999,19 +984,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>101,6 cm</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>127 cm</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -1021,52 +996,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Angelica_Kauffmann_%281741-1807%29_-_Self_Portrait_of_the_Artist_Hesitating_between_the_Arts_of_Music_and_Painting_-_960079_-_National_Trust.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c0/Fran%C3%A7ois_Boucher_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Angelica</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KAUFFMAN</t>
+          <t>BOUCHER</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1791-1794</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yorkshire</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nostell Priory</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>"Autoportrait hésitant entre la musique et la peinture"</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>"Self-Portrait Hesitating between the Arts of Music and Painting"</t>
+          <t>"Le Déjeuner"</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1076,67 +1046,67 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>147,3 cm</t>
+          <t>81,5 cm</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>216,5 cm</t>
+          <t>65,5 cm</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Girodet_-_Sommeil_Endymion.jpg/1280px-Girodet_-_Sommeil_Endymion.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/cf/Fran%C3%A7ois_Boucher%2C_The_Love_Letter%2C_1750%2C_NGA_46027FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anne-Louis</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIRODET</t>
+          <t>BOUCHER</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>"Le Sommeil d’Endymion"</t>
+          <t>"La Lettre d'amour"</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1144,74 +1114,59 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>198 cm</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>261 cm</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Anton_Graff_-_Friedrich_Schiller.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GRAFF</t>
+          <t>BOUCHER</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1786-1791</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Dresde</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Galerie d'art</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>"Portrait de Friedrich Schiller"</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>"Bildnis Friedrich Schiller"</t>
+          <t>"Diane sortant du bain"</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1219,204 +1174,239 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>56 cm</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>73 cm</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Anton_Raphael_Mengs_-_Parnassus_%28FondazioneTorlonia%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Madame_de_Pompadour.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anton Raphael</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MENGS</t>
+          <t>BOUCHER</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Villa Albani</t>
+          <t>Alte Pinakothek</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>"Le Parnasse"</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>"Der Parnass"</t>
+          <t>"Madame de Pompadour"</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>201 cm</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>157 cm</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Anton_Raphael_Mengs_-_Self-Portrait_-_WGA15040.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anton Raphael</t>
+          <t>Giovanni Antonio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MENGS</t>
+          <t>CANAL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CANALETTO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CANALETTO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Musée de l'Ermitage</t>
+          <t>Museum of Fine Arts</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
+          <t>"Le Bassin de San Marco"</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>"Selbstbildnis"</t>
+          <t>"Bacino di San Marco"</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>46 cm</t>
+          <t>125 cm</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>38 cm</t>
+          <t>204 cm</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/The_Death_of_General_Wolfe_B.West%2C1770.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Giovanni Antonio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>CANAL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CANALETTO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CANALETTO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ottawa</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>National Gallery of Canada</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>"La Mort du général Wolfe"</t>
+          <t>"La Piazza San Marco"</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>"The Death of General Wolfe"</t>
+          <t>"Piazza San Marco"</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1424,94 +1414,84 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>152,6 cm</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>214,5 cm</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Benjamin_West_003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/ca/Rosalba_Carriera_Self-portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Rosalba</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>CARRIERA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1771-1772</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Philadelphie</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pennsylvania Academy of the Fine Arts</t>
+          <t>Galerie des Offices</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>"Guillaume Penn et les Indiens"</t>
+          <t>"Autoportrait"</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>"Penn's Treaty with the Indians"</t>
+          <t>"Autoritratto"</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>191,8 cm</t>
+          <t>46 cm</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>273,7 cm</t>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U15" t="n">
@@ -1521,34 +1501,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/02/Canaletto_-_Dresden_seen_from_the_Right_Bank_of_the_Elbe%2C_beneath_the_Augusts_Bridge_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/47/Rosalba_Carriera_-_Young_Girl_Holding_a_Monkey_-_WGA04508.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Rosalba</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BELLOTTO</t>
+          <t>CARRIERA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1757</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>1721</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1780</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1748</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Dresde</t>
@@ -1561,17 +1541,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>"Vue de Dresde depuis la rive droite de l'Elbe"</t>
+          <t>"Portrait de jeune fille au singe"</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>"Dresda vista dalla riva destra dell'Elba"</t>
+          <t>"Ritratto di fanciulla con scimmietta"</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1586,47 +1566,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Bellotto_View_of_Warsaw_from_Praga.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/94/La_Raie_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3197.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Jean-Baptiste-Siméon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BELLOTTO</t>
+          <t>CHARDIN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Musée national de Varsovie</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>"Vue de Varsovie depuis Praga"</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>"Veduta di Varsavia dalla Praga"</t>
+          <t>"La Raie"</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1634,159 +1614,139 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>114,5 cm</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>146 cm</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg/1280px-Boston%2C_Museum_of_Fine_Art_-_Il_bacino_di_San_Marco_c.1738_-_Canaletto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Chardin_pastel_selfportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Giovanni Antonio</t>
+          <t>Jean-Baptiste-Siméon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CANAL</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CANALETTO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CANALETTO</t>
+          <t>CHARDIN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Museum of Fine Arts</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>"Le Bassin de San Marco"</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>"Bacino di San Marco"</t>
+          <t>"Autoportrait"</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>125 cm</t>
+          <t>46 cm</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>204 cm</t>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg/1280px-Giovanni_Antonio_Canal%2C_il_Canaletto_-_Piazza_San_Marco_-_WGA03883.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/ab/Jean_Sim%C3%A9on_Chardin_-_Water_Glass_and_Jug_-_WGA04775.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Giovanni Antonio</t>
+          <t>Jean-Baptiste-Siméon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CANAL</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CANALETTO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CANALETTO</t>
+          <t>CHARDIN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Carnegie Museum of Art</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>"La Piazza San Marco"</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>"Piazza San Marco"</t>
+          <t>"Nature morte au verre d'eau et à la cafetière"</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1794,59 +1754,69 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>32,5 cm</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>41 cm</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/26/Soap_Bubbles_LACMA_M.79.251.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carle</t>
+          <t>Jean-Baptiste-Siméon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>van LOO</t>
+          <t>CHARDIN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1733-1734</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>"Halte de chasse"</t>
+          <t>"Les Bulles de savon"</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1856,12 +1826,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>216 cm</t>
+          <t>93 cm</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>276 cm</t>
+          <t>74,6 cm</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -1870,53 +1840,58 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Une_sultane_buvant_du_caf%C3%A9_Carle_Van_Loo_ch%C3%A2teau_de_Bellevue.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Watsonandtheshark-original.jpg/1280px-Watsonandtheshark-original.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carle</t>
+          <t>John Singleton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>van LOO</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Musée de l'Ermitage</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>"La Sultane prenant du café"</t>
+          <t>"Watson et le requin"</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>"Watson and the Shark"</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1924,9 +1899,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>182,1 cm</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>229,7 cm</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -1936,47 +1921,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg/960px-Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Charles Willson</t>
+          <t>Jacques-Louis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PEALE</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1784</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Princeton University Art Museum</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>"George Washington à Princeton"</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>"George Washington at Princeton"</t>
+          <t>"Le Serment des Horaces"</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1986,132 +1971,137 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>238,8 cm</t>
+          <t>330 cm</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>147,3 cm</t>
+          <t>425 cm</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/18/Benjamin_Franklin%2C_by_Charles_Willson_Peale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/David_Self_Portrait.jpg/960px-David_Self_Portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Charles Willson</t>
+          <t>Jacques-Louis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PEALE</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>"Portrait de Benjamin Franklin"</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>"Portrait of Benjamin Franklin"</t>
+          <t>"Autoportrait"</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>46 cm</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/4e/Deuxieme_vue_du_port_de_Bordeaux_prise_du_ch%C3%A2teau_Trompette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Jacques-Louis_David_002.jpg/960px-Jacques-Louis_David_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claude Joseph</t>
+          <t>Jacques-Louis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VERNET</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bruxelles</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Musée national de la Marine</t>
+          <t>Musées royaux des Beaux-Arts de Belgique</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>"Vue du port de Bordeaux"</t>
+          <t>"La Mort de Marat"</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2126,7 +2116,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>263 cm</t>
+          <t>128 cm</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2135,58 +2125,53 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg/1280px-Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/87/Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg/1280px-Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Claude Joseph</t>
+          <t>Jacques-Louis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VERNET</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1772</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Washington</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Château de Versailles</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>"Un naufrage"</t>
+          <t>"Le Serment du Jeu de Paume"</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Dessin à la plume et lavis (inachevé)</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2195,53 +2180,53 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg/1280px-The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Claude Joseph</t>
+          <t>Jacques-Louis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VERNET</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>"La Tempête"</t>
+          <t>"L'Enlèvement des Sabines"</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2249,64 +2234,74 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>385 cm</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>522 cm</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Dmitry_Levitzky%2C_Denis_Diderot%2C_1773%2C_Mus%C3%A9e_d%27Art_et_Histoire_de_Gen%C3%A8ve_1829-0009.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/El_Quitasol_%28Goya%29.jpg/1280px-El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dmitri</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LEVITZKY</t>
+          <t>de GOYA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1773-1774</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Genève</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Musée d'art et d'histoire</t>
+          <t>Museo del Prado</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>"Portrait de Denis Diderot"</t>
+          <t>"Le Parasol"</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>"Portret Deni Didro (Портрет Дени Дидро)"</t>
+          <t>"El Quitasol"</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2314,59 +2309,74 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>104 cm</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>152 cm</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/da/Goya.pelele.prado.jpg/960px-Goya.pelele.prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Élisabeth</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VIGÉE LE BRUN</t>
+          <t>de GOYA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1782-1783</t>
+          <t>1791-1792</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Museo del Prado</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>"Autoportrait au chapeau de paille"</t>
+          <t>"Le Mannequin de paille"</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>"El Pelele"</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2376,62 +2386,72 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>97,8 cm</t>
+          <t>267 cm</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>70,5 cm</t>
+          <t>160 cm</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Francisco_de_Goya_y_Lucientes_-_Witches%27_Sabbath_-_WGA10007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Élisabeth</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VIGÉE LE BRUN</t>
+          <t>de GOYA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1797-1798</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Château de Versailles</t>
+          <t>Museo Lázaro Galdiano</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>"Marie-Antoinette avec une rose"</t>
+          <t>"Le Sabbat des sorcières"</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>"El Aquelarre"</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2441,152 +2461,162 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>113 cm</t>
+          <t>43 cm</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>87 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/3e/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg/960px-%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Élisabeth</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VIGÉE LE BRUN</t>
+          <t>de GOYA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Agen</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>"Autoportrait avec sa fille Julie"</t>
+          <t>"Autoportrait"</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>"Autorretrato"</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Huile sur bois</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>130 cm</t>
+          <t>46 cm</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>94 cm</t>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/11/Ivan_Orlov_1765_rokotov.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/88/Maurice_Quentin_de_La_Tour_-_Marquise_de_Pompadour_-_WGA12359.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fiodor</t>
+          <t>Maurice Quentin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ROKOTOV</t>
+          <t>de la TOUR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>environ 1735</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1762-1763</t>
+          <t>1748-1755</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Moscou</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Galerie Tretiakov</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>"Portrait du comte Orlov"</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>"Portret grafa Orlova (Портрет графа Орлова)"</t>
+          <t>"Portrait de Madame de Pompadour"</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>175 cm</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>128 cm</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U31" t="n">
@@ -2596,32 +2626,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/96/Guardi_-_Le_D%C3%A9part_du_Bucentaure_vers_le_Lido_de_Venise%2C_le_jour_de_l%27Ascension%2C_vers_1770_-_1780%2C_INV_20009.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/2d/Maurice_Quentin_de_La_Tour_-_Portrait_de_Jean_Le_Rond_d%27Alembert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Maurice Quentin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GUARDI</t>
+          <t>de la TOUR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1775-1780</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2636,32 +2666,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>"Le Doge sur le Bucentaure près de la Riva di Sant'Elena"</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>"Il Doge sul Bucintoro presso la Riva di Sant'Elena"</t>
+          <t>"Portrait de d'Alembert"</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>67 cm</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>100 cm</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U32" t="n">
@@ -2671,52 +2686,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Edinburgh_NGS_Guardi_Piazza_san_Marco.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg/960px-Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GUARDI</t>
+          <t>de LARGILLIÈRE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1775-1780</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Edimbourg</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Galeries nationales d’Écosse</t>
+          <t>Château de Versailles</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>"La Piazza San Marco"</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>"Piazza San Marco"</t>
+          <t>"Portrait de Voltaire jeune"</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2726,7 +2731,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U33" t="n">
@@ -2736,32 +2741,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/El_Quitasol_%28Goya%29.jpg/1280px-El_Quitasol_%28Goya%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/47/Madame_de_Pompadour_by_Fran%C3%A7ois-Hubert_Drouais.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>François-Hubert</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>de GOYA</t>
+          <t>DROUAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2771,17 +2776,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Museo del Prado</t>
+          <t>Musée du Prado</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>"Le Parasol"</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>"El Quitasol"</t>
+          <t>"Madame du Barry"</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2789,74 +2789,59 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>104 cm</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>152 cm</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/da/Goya.pelele.prado.jpg/960px-Goya.pelele.prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/79/Le-discret-by-ducreux.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>de GOYA</t>
+          <t>DUCREUX</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1791-1792</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Museo del Prado</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>"Le Mannequin de paille"</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>"El Pelele"</t>
+          <t>"Le Discret"</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2864,74 +2849,59 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>267 cm</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>160 cm</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Francisco_de_Goya_y_Lucientes_-_Witches%27_Sabbath_-_WGA10007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg/960px-Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>de GOYA</t>
+          <t>DUCREUX</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1797-1798</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Museo Lázaro Galdiano</t>
+          <t>The J. Paul Getty Museum</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>"Le Sabbat des sorcières"</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>"El Aquelarre"</t>
+          <t>"Autoportrait en bâilleur"</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -2939,144 +2909,119 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>43 cm</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>30 cm</t>
-        </is>
-      </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg/960px-%28Agen%29_Autorretrato_de_Goya_%281783%29_-_Mus%C3%A9e_des_Beaux-Arts_d%27Agen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/VAlfieriFabre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>François-Xavier</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>de GOYA</t>
+          <t>FABRE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Agen</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Galerie des Offices</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>"Autorretrato"</t>
+          <t>"Portrait du comte Vittorio Alfieri"</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pastel</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>46 cm</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>38 cm</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c0/Fran%C3%A7ois_Boucher_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/43/Joean_Honor%C3%A9_Fragonard_-_The_Swing.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Jean-Honoré</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BOUCHER</t>
+          <t>FRAGONARD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Wallace Collection</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>"Le Déjeuner"</t>
+          <t>"Les Hasards heureux de l'escarpolette"</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3086,12 +3031,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>81,5 cm</t>
+          <t>81 cm</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>65,5 cm</t>
+          <t>64,2 cm</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -3106,52 +3051,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/cf/Fran%C3%A7ois_Boucher%2C_The_Love_Letter%2C_1750%2C_NGA_46027FXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/dc/Jean-Honor%C3%A9_Fragonard_009.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Jean-Honoré</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BOUCHER</t>
+          <t>FRAGONARD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>"La Lettre d'amour"</t>
+          <t>"Le Verrou"</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>73 cm</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>93 cm</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3166,47 +3121,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6d/Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg/1280px-Diane_sortant_du_bain_-_Fran%C3%A7ois_Boucher_-_Mus%C3%A9e_du_Louvre_Peintures_INV_2712.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Fragonard%2C_The_Reader.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Jean-Honoré</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BOUCHER</t>
+          <t>FRAGONARD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1770-1772</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>"Diane sortant du bain"</t>
+          <t>"La Liseuse"</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3216,12 +3171,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>56 cm</t>
+          <t>81,1 cm</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>73 cm</t>
+          <t>64,8 cm</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -3236,47 +3191,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/82/Madame_de_Pompadour.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/9d/Jean-Honor%C3%A9_Fragonard_-_The_Stolen_Kiss.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Jean-Honoré</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOUCHER</t>
+          <t>FRAGONARD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1786-1788</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Alte Pinakothek</t>
+          <t>Musée de l'Ermitage</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>"Madame de Pompadour"</t>
+          <t>"Le Baiser à la dérobée"</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3286,12 +3241,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>201 cm</t>
+          <t>45 cm</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>157 cm</t>
+          <t>55 cm</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -3306,47 +3261,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/47/Madame_de_Pompadour_by_Fran%C3%A7ois-Hubert_Drouais.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>François-Hubert</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DROUAIS</t>
+          <t>FUSELI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Madrid</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Musée du Prado</t>
+          <t>Detroit Institute of Arts</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>"Madame du Barry"</t>
+          <t>"Le Cauchemar"</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>"The Nightmare"</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3354,9 +3309,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>101,6 cm</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>126,7 cm</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U42" t="n">
@@ -3366,47 +3331,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/VAlfieriFabre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg/1280px-Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>François-Xavier</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FABRE</t>
+          <t>FUSELI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Galerie des Offices</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>"Portrait du comte Vittorio Alfieri"</t>
+          <t>"Titania et Bottom"</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3414,9 +3379,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>217,2 cm</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>275,6 cm</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U43" t="n">
@@ -3426,47 +3401,52 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Whistlejacket_by_George_Stubbs.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg/960px-Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STUBBS</t>
+          <t>FUSELI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>"Whistlejacket"</t>
+          <t>"Lady Macbeth somnambule"</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>"Lady Macbeth Sleepwalking"</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3474,19 +3454,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>292 cm</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>246,4 cm</t>
-        </is>
-      </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U44" t="n">
@@ -3496,52 +3466,52 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/36/George_Stubbs_-_A_Lion_Attacking_a_Horse_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Thomas_Gainsborough_-_Mr_and_Mrs_Andrews.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>STUBBS</t>
+          <t>GAINSBOROUGH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>New Haven</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Yale Center for British Art</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>"Un lion attaquant un cheval"</t>
+          <t>"Monsieur et Madame Andrews"</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>"A Lion Attacking a Horse"</t>
+          <t>"Mr and Mrs Andrews"</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3549,64 +3519,74 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>69,8 cm</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>119,4 cm</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr">
         <is>
           <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Thomas_Gainsborough_-_The_Blue_Boy_%28The_Huntington_Library%2C_San_Marino_L._A.%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>STUART</t>
+          <t>GAINSBOROUGH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Californie</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>National Portrait Gallery</t>
+          <t>The Huntington</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>"Portrait de George Washington (Lansdowne)"</t>
+          <t>"Le Garçon bleu"</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>"George Washington (Lansdowne Portrait)"</t>
+          <t>"The Blue Boy"</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3616,72 +3596,67 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>247,6 cm</t>
+          <t>178 cm</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>158,7 cm</t>
+          <t>122 cm</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/Giambattista_Tiepolo_-_The_Banquet_of_Cleopatra_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Girodet_-_Sommeil_Endymion.jpg/1280px-Girodet_-_Sommeil_Endymion.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Giovanni Battista</t>
+          <t>Anne-Louis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TIEPOLO</t>
+          <t>GIRODET</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1743-1744</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Melbourne</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>National Gallery of Victoria</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>"Le Banquet de Cléopâtre"</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>"Il Banchetto di Cleopatra"</t>
+          <t>"Le Sommeil d’Endymion"</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3691,17 +3666,17 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>248,2 cm</t>
+          <t>198 cm</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>357 cm</t>
+          <t>261 cm</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U47" t="n">
@@ -3711,57 +3686,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/03/Giovanni_Battista_Tiepolo_-_Apollo_and_the_Continents_-_WGA22323.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Anton_Graff_-_Friedrich_Schiller.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Giovanni Battista</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TIEPOLO</t>
+          <t>GRAFF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1752-1753</t>
+          <t>1786-1791</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Dresde</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Résidence de Wurtzbourg</t>
+          <t>Galerie d'art</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>"Apollon et les Continents (fresque de l'escalier)"</t>
+          <t>"Portrait de Friedrich Schiller"</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>"Apollo e i Continenti"</t>
+          <t>"Bildnis Friedrich Schiller"</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fresque</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U48" t="n">
@@ -3771,107 +3751,117 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d4/The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg/960px-The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Jean-Baptiste_Greuze_-_The_Village_Agreement.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LANG SHINING</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>GIUSEPPE CASTIGLIONE</t>
+          <t>GREUZE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Pékin</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Musée du Palais</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>"Portrait de l'empereur Qianlong en armure"</t>
+          <t>"L'Accordée de village"</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Encre et couleurs sur soie</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>92 cm</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>117 cm</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>chinoise</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/John_Henry_Fuseli_-_The_Nightmare.JPG/1280px-John_Henry_Fuseli_-_The_Nightmare.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Jean-Baptiste_Greuze_-_The_Punished_Son.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FUSELI</t>
+          <t>GREUZE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Detroit Institute of Arts</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>"Le Cauchemar"</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>"The Nightmare"</t>
+          <t>"Le Fils puni"</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -3881,67 +3871,72 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>101,6 cm</t>
+          <t>130 cm</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>126,7 cm</t>
+          <t>163 cm</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg/1280px-Henry_Fuseli_-_Titania_and_Bottom_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/96/Guardi_-_Le_D%C3%A9part_du_Bucentaure_vers_le_Lido_de_Venise%2C_le_jour_de_l%27Ascension%2C_vers_1770_-_1780%2C_INV_20009.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FUSELI</t>
+          <t>GUARDI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1775-1780</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>"Titania et Bottom"</t>
+          <t>"Le Doge sur le Bucentaure près de la Riva di Sant'Elena"</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>"Il Doge sul Bucintoro presso la Riva di Sant'Elena"</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3951,17 +3946,17 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>217,2 cm</t>
+          <t>67 cm</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>275,6 cm</t>
+          <t>100 cm</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U51" t="n">
@@ -3971,52 +3966,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg/960px-Lady_Macbeth_somnambule_-_Johann_Heinrich_F%C3%BCssli_-_Mus%C3%A9e_du_Louvre_Peintures_RF_1970_29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Edinburgh_NGS_Guardi_Piazza_san_Marco.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FUSELI</t>
+          <t>GUARDI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1775-1780</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Edimbourg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Galeries nationales d’Écosse</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>"Lady Macbeth somnambule"</t>
+          <t>"La Piazza San Marco"</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>"Lady Macbeth Sleepwalking"</t>
+          <t>"Piazza San Marco"</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4026,7 +4021,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>suisse</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U52" t="n">
@@ -4036,52 +4031,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/cb/Reverend_Robert_Walker_%281755_-_1808%29_Skating_on_Duddingston_Loch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/William_Hogarth_038.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RAEBURN</t>
+          <t>HOGARTH</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Édimbourg</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>National Gallery of Scotland</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>"Le Révérend Robert Walker patinant"</t>
+          <t>"Le Mariage à la mode (I - Le Contrat de mariage)"</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>"The Reverend Robert Walker Skating"</t>
+          <t>"Marriage A-la-Mode: 1, The Marriage Settlement"</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4091,67 +4086,72 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>76,2 cm</t>
+          <t>69,9 cm</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>63,5 cm</t>
+          <t>90,8 cm</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>écossaise (Royaume-Uni)</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Henry_Raeburn_%281756-1823%29_-_Sir_John_Sinclair_%281754%E2%80%931835%29%2C_1st_Baronet_of_Ulbster_-_NG_2301_-_National_Galleries_of_Scotland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/William_Hogarth_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RAEBURN</t>
+          <t>HOGARTH</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1794-1799</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Édimbourg</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>National Galleries of Scotland</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>"Sir John Sinclair"</t>
+          <t>"Le Peintre et son carlin (autoportrait au chien Trump)"</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>"The Painter and his Pug"</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4159,139 +4159,154 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>69,9 cm</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>écossaise (Royaume-Uni)</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/27/Hua_Yan_-_Birds_and_Flowers_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/03/William_Hogarth_047.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yan</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HUA</t>
+          <t>HOGARTH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Freer Gallery of Art (National Museum of Asian Art)</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>"Oiseaux et fleurs"</t>
+          <t>"Les Enfants Graham"</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>"The Graham Children"</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Encre et couleurs sur papier</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>162,5 cm</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>181 cm</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>chinoise</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/56/Hubert_Robert_-_Imaginary_View_of_the_Grande_Galerie_in_the_Louvre_in_Ruins_-_WGA19589.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/27/Hua_Yan_-_Birds_and_Flowers_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hubert</t>
+          <t>Yan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ROBERT</t>
+          <t>HUA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Freer Gallery of Art (National Museum of Asian Art)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>"Le Louvre en ruines"</t>
+          <t>"Oiseaux et fleurs"</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>114 cm</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>146 cm</t>
+          <t>Encre et couleurs sur papier</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>chinoise</t>
         </is>
       </c>
       <c r="U56" t="n">
@@ -4361,47 +4376,52 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg/1280px-Le_Serment_des_Horaces_-_Jacques-Louis_David_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3692_%3B_MR_1432.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Kauffmann_Cornelia_mater_Gracchorum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jacques-Louis</t>
+          <t>Angelica</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>KAUFFMAN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Virginia Museum of Fine Arts</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>"Le Serment des Horaces"</t>
+          <t>"Cornelia, mère des Gracques"</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>"Cornelia, Mother of the Gracchi"</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -4411,137 +4431,142 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>330 cm</t>
+          <t>101,6 cm</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>425 cm</t>
+          <t>127 cm</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/David_Self_Portrait.jpg/960px-David_Self_Portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a3/Angelica_Kauffmann_%281741-1807%29_-_Self_Portrait_of_the_Artist_Hesitating_between_the_Arts_of_Music_and_Painting_-_960079_-_National_Trust.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jacques-Louis</t>
+          <t>Angelica</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>KAUFFMAN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1791-1794</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Yorkshire</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Nostell Priory</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
+          <t>"Autoportrait hésitant entre la musique et la peinture"</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>"Self-Portrait Hesitating between the Arts of Music and Painting"</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>46 cm</t>
+          <t>147,3 cm</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>38 cm</t>
+          <t>216,5 cm</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>suisse</t>
         </is>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Jacques-Louis_David_002.jpg/960px-Jacques-Louis_David_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/8a/Ad%C3%A9la%C3%AFde_Labille-Guiard_-_Self-Portrait_with_Two_Pupils_-_The_Metropolitan_Museum_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jacques-Louis</t>
+          <t>Adélaïde</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>LABILLE-GUIARD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Bruxelles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Musées royaux des Beaux-Arts de Belgique</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>"La Mort de Marat"</t>
+          <t>"Autoportrait avec deux élèves"</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -4551,12 +4576,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>165 cm</t>
+          <t>210,8 cm</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>128 cm</t>
+          <t>151,1 cm</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -4565,53 +4590,58 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/87/Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg/1280px-Serment_du_Jeu_de_Paume_-_Jacques-Louis_David.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/19/Labille-Guiard_Robespierre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jacques-Louis</t>
+          <t>Adélaïde</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>LABILLE-GUIARD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1786</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Château de Versailles</t>
+          <t>Musée Carnavalet</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>"Le Serment du Jeu de Paume"</t>
+          <t>"Portrait de Robespierre"</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Dessin à la plume et lavis (inachevé)</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -4620,53 +4650,48 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg/1280px-The_Intervention_of_the_Sabine_Women_-_David_%28Louvre_INV_3691%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/D%C3%A9jeuner_de_jambon_-_Nicolas_Lancret_-_mus%C3%A9e_Cond%C3%A9.jpg/960px-D%C3%A9jeuner_de_jambon_-_Nicolas_Lancret_-_mus%C3%A9e_Cond%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jacques-Louis</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>LANCRET</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1799</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Château de Chantilly</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>"L'Enlèvement des Sabines"</t>
+          <t>"Le Déjeuner de jambon"</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -4674,139 +4699,124 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>385 cm</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>522 cm</t>
-        </is>
-      </c>
       <c r="T62" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Jean-Antoine</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d4/The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg/960px-The_Qianlong_Emperor_in_Ceremonial_Armour_on_Horseback.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WATTEAU</t>
+          <t>LANG SHINING</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>GIUSEPPE CASTIGLIONE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Pékin</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Musée du Palais</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>"Le Pèlerinage à l'île de Cythère"</t>
+          <t>"Portrait de l'empereur Qianlong en armure"</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>129 cm</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>194 cm</t>
+          <t>Encre et couleurs sur soie</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>chinoise</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/Jean-Antoine_Watteau_-_Pierrot%2C_dit_autrefois_GillesFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Portrait_of_Elizabeth_Farren%2C_by_Thomas_Lawrence.jpg/960px-Portrait_of_Elizabeth_Farren%2C_by_Thomas_Lawrence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jean-Antoine</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WATTEAU</t>
+          <t>LAWRENCE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1718-1719</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>"Pierrot, dit autrefois Gilles"</t>
+          <t>"Portrait d’Elizabeth Farren "</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>"Portrait of Elizabeth Farren"</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -4816,67 +4826,72 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>184,5 cm</t>
+          <t>238,8 cm</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>149,5 cm</t>
+          <t>146,7 cm</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c7/L%27enseigne_de_Gersaint.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/75/Dmitry_Levitzky%2C_Denis_Diderot%2C_1773%2C_Mus%C3%A9e_d%27Art_et_Histoire_de_Gen%C3%A8ve_1829-0009.jpeg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jean-Antoine</t>
+          <t>Dmitri</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WATTEAU</t>
+          <t>LEVITZKY</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1773-1774</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Genève</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Schloss Charlottenburg</t>
+          <t>Musée d'art et d'histoire</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>"L'Enseigne de Gersaint"</t>
+          <t>"Portrait de Denis Diderot"</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>"Portret Deni Didro (Портрет Дени Дидро)"</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -4884,84 +4899,74 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>166 cm</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>306 cm</t>
-        </is>
-      </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/b8/Jean-Antoine_Watteau_-_L%27indiff%C3%A9rent.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Jean-Etienne_Liotard_-_The_Chocolate_Girl_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jean-Antoine</t>
+          <t>Jean-Étienne</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WATTEAU</t>
+          <t>LIOTARD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Dresde</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Gemäldegalerie</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>"L'Indifférent"</t>
+          <t>"La Belle Chocolatière"</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel sur parchemin</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>25,5 cm</t>
+          <t>82,5 cm</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>19 cm</t>
+          <t>52,5 cm</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -4970,68 +4975,58 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Jean-Antoine_Watteau_-_Mezzetin.JPG/960px-Jean-Antoine_Watteau_-_Mezzetin.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Femme_turque_avec_servante_%281742-1743%29_-_Jean-%C3%89tienne_Liotard_%28MAH%2C_Geneva%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jean-Antoine</t>
+          <t>Jean-Étienne</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WATTEAU</t>
+          <t>LIOTARD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1718-1720</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Genève</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Musée d’art et d’histoire</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>"Le Mezzetin"</t>
+          <t>"Une femme turque avec sa servante"</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>55,2 cm</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>43,2 cm</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -5040,53 +5035,58 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Jean-Baptiste_Greuze_-_The_Village_Agreement.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg/960px-Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GREUZE</t>
+          <t>LONGHI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Ca' Rezzonico</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>"L'Accordée de village"</t>
+          <t>"Le Rhinocéros"</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>"Il Rinoceronte"</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5096,67 +5096,72 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>92 cm</t>
+          <t>62 cm</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>117 cm</t>
+          <t>50 cm</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Jean-Baptiste_Greuze_-_The_Punished_Son.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Ballando_lesson_by_Pietro_Longhi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GREUZE</t>
+          <t>LONGHI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Ca' Rezzonico</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>"Le Fils puni"</t>
+          <t>"La Leçon de danse"</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>"La Lezione di danza"</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5166,67 +5171,72 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>130 cm</t>
+          <t>61 cm</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>163 cm</t>
+          <t>49 cm</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Jean-Baptiste_Oudry_-_Dead_Roe_-_WGA16777.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/%27The_Tame_Magpie%27%2C_oil_on_canvas_painting_by_Alessandro_Magnasco%2C_c._1707-8%2C_Metropolitan_Museum_of_Art.JPG/1280px-%27The_Tame_Magpie%27%2C_oil_on_canvas_painting_by_Alessandro_Magnasco%2C_c._1707-8%2C_Metropolitan_Museum_of_Art.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Alessandro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OUDRY</t>
+          <t>MAGNASCO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1707-1708</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Wallace Collection</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>"Le chevreuil mort"</t>
+          <t>"La Pie apprivoisée"</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>"La Gazza ammaestrata"</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -5234,19 +5244,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>c.120 cm</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>c.100 cm</t>
-        </is>
-      </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U70" t="n">
@@ -5256,52 +5256,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg/1280px-Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/%27Sitting_Tiger%27_by_Maruyama_Okyo%2C_1777%2C_Minneapolis_Institute_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Ōkyo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OUDRY</t>
+          <t>MARUYAMA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Musée d’Arts de Nantes</t>
+          <t>Minneapolis Institute of Art</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>"La Chasse au loup"</t>
+          <t>"Tigre assis"</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Encre et couleurs sur soie</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>japonaise</t>
         </is>
       </c>
       <c r="U71" t="n">
@@ -5311,57 +5311,62 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/39/Jean-Baptiste_Perronneau_-_Portrait_of_a_Boy_with_a_Book_-_WGA17219.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Nature_morte_aux_figues%2C_par_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PERRONNEAU</t>
+          <t>MELÉNDEZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Saint Pétersbourg</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Musée de l'Ermitage</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>"Garçon au livre"</t>
+          <t>"Nature morte aux figues"</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>"Bodegón de higos"</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U72" t="n">
@@ -5371,32 +5376,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/94/La_Raie_-_Jean_Baptiste_Sim%C3%A9on_Chardin_-_Mus%C3%A9e_du_Louvre_Peintures_INV_3197.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Self-portrait_Holding_an_Academic_Study_by_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jean-Baptiste-Siméon</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CHARDIN</t>
+          <t>MELÉNDEZ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5411,52 +5416,57 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>"La Raie"</t>
+          <t>"Autoportrait"</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>"Autorretrato"</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>114,5 cm</t>
+          <t>46 cm</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>146 cm</t>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>espagnole</t>
         </is>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Chardin_pastel_selfportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Anton_Raphael_Mengs_-_Parnassus_%28FondazioneTorlonia%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jean-Baptiste-Siméon</t>
+          <t>Anton Raphael</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CHARDIN</t>
+          <t>MENGS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5466,67 +5476,62 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Villa Albani</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
+          <t>"Le Parnasse"</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>"Der Parnass"</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Pastel</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>46 cm</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>38 cm</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/ab/Jean_Sim%C3%A9on_Chardin_-_Water_Glass_and_Jug_-_WGA04775.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Anton_Raphael_Mengs_-_Self-Portrait_-_WGA15040.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jean-Baptiste-Siméon</t>
+          <t>Anton Raphael</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CHARDIN</t>
+          <t>MENGS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5536,92 +5541,92 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Carnegie Museum of Art</t>
+          <t>Musée de l'Ermitage</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>"Nature morte au verre d'eau et à la cafetière"</t>
+          <t>"Autoportrait"</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>"Selbstbildnis"</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>32,5 cm</t>
+          <t>46 cm</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>41 cm</t>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/26/Soap_Bubbles_LACMA_M.79.251.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/9/95/Natoire_-_Psych%C3%A9_%C3%A0_sa_toilette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jean-Baptiste-Siméon</t>
+          <t>Charles-Joseph</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHARDIN</t>
+          <t>NATOIRE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1733-1734</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>New York</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Musée d’Art de La Nouvelle-Orléans</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>"Les Bulles de savon"</t>
+          <t>"Psyché à sa toilette"</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -5629,84 +5634,59 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>93 cm</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>74,6 cm</t>
-        </is>
-      </c>
       <c r="T76" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Jean-Etienne_Liotard_-_The_Chocolate_Girl_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/6a/Jean-Marc_Nattier%2C_Madame_de_Pompadour_en_Diane_%281746%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jean-Étienne</t>
+          <t>Jean-Marc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LIOTARD</t>
+          <t>NATTIER</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Dresde</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Gemäldegalerie</t>
+          <t>Château de Versailles</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>"La Belle Chocolatière"</t>
+          <t>"Madame de Pompadour en Diane"</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Pastel sur parchemin</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>82,5 cm</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>52,5 cm</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -5721,52 +5701,62 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Femme_turque_avec_servante_%281742-1743%29_-_Jean-%C3%89tienne_Liotard_%28MAH%2C_Geneva%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Jean-Baptiste_Oudry_-_Dead_Roe_-_WGA16777.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jean-Étienne</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LIOTARD</t>
+          <t>OUDRY</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Genève</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Musée d’art et d’histoire</t>
+          <t>Wallace Collection</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>"Une femme turque avec sa servante"</t>
+          <t>"Le chevreuil mort"</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>c.120 cm</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>c.100 cm</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -5781,47 +5771,42 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/43/Joean_Honor%C3%A9_Fragonard_-_The_Swing.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg/1280px-Jean-Baptiste_Oudry_-_Chasse_au_loup_en_for%C3%AAt_%281748%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jean-Honoré</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FRAGONARD</t>
+          <t>OUDRY</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Londres</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Wallace Collection</t>
+          <t>Musée d’Arts de Nantes</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>"Les Hasards heureux de l'escarpolette"</t>
+          <t>"La Chasse au loup"</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -5829,69 +5814,59 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>64,2 cm</t>
-        </is>
-      </c>
       <c r="T79" t="inlineStr">
         <is>
           <t>française</t>
         </is>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/dc/Jean-Honor%C3%A9_Fragonard_009.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg/960px-Charles_Willson_Peale_-_George_Washington_at_the_Battle_of_Princeton_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jean-Honoré</t>
+          <t>Charles Willson</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FRAGONARD</t>
+          <t>PEALE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1777</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Princeton University Art Museum</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>"Le Verrou"</t>
+          <t>"George Washington à Princeton"</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>"George Washington at Princeton"</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -5901,52 +5876,52 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>73 cm</t>
+          <t>238,8 cm</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>93 cm</t>
+          <t>147,3 cm</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/69/Fragonard%2C_The_Reader.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/18/Benjamin_Franklin%2C_by_Charles_Willson_Peale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jean-Honoré</t>
+          <t>Charles Willson</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FRAGONARD</t>
+          <t>PEALE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1770-1772</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5961,7 +5936,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>"La Liseuse"</t>
+          <t>"Portrait de Benjamin Franklin"</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>"Portrait of Benjamin Franklin"</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -5969,59 +5949,49 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>81,1 cm</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>64,8 cm</t>
-        </is>
-      </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/9d/Jean-Honor%C3%A9_Fragonard_-_The_Stolen_Kiss.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/39/Jean-Baptiste_Perronneau_-_Portrait_of_a_Boy_with_a_Book_-_WGA17219.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jean-Honoré</t>
+          <t>Jean-Baptiste</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FRAGONARD</t>
+          <t>PERRONNEAU</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1786-1788</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Saint-Pétersbourg</t>
+          <t>Saint Pétersbourg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6031,22 +6001,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>"Le Baiser à la dérobée"</t>
+          <t>"Garçon au livre"</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>45 cm</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>55 cm</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -6055,48 +6015,58 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/6a/Jean-Marc_Nattier%2C_Madame_de_Pompadour_en_Diane_%281746%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/cb/Reverend_Robert_Walker_%281755_-_1808%29_Skating_on_Duddingston_Loch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jean-Marc</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NATTIER</t>
+          <t>RAEBURN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Édimbourg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Château de Versailles</t>
+          <t>National Gallery of Scotland</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>"Madame de Pompadour en Diane"</t>
+          <t>"Le Révérend Robert Walker patinant"</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>"The Reverend Robert Walker Skating"</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -6104,9 +6074,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>76,2 cm</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>63,5 cm</t>
+        </is>
+      </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>écossaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U83" t="n">
@@ -6116,52 +6096,47 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/6e/Henry_Raeburn_%281756-1823%29_-_Sir_John_Sinclair_%281754%E2%80%931835%29%2C_1st_Baronet_of_Ulbster_-_NG_2301_-_National_Galleries_of_Scotland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Johann</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ZOFFANY</t>
+          <t>RAEBURN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1772-1778</t>
+          <t>1794-1799</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Édimbourg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Royal Collection</t>
+          <t>National Galleries of Scotland</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>"La Tribune des Offices"</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>"The Tribuna of the Uffizi"</t>
+          <t>"Sir John Sinclair"</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -6169,19 +6144,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>123,5 cm</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>155 cm</t>
-        </is>
-      </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>écossaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U84" t="n">
@@ -6191,32 +6156,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/ca/The_Portraits_of_the_Academicians_of_the_Royal_Academy%2C_1771-72%2C_oil_on_canvas%2C_The_Royal_Collection_by_Johan_Zoffany.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Allan_Ramsay_%281713-84%29_-_George_III_%281738-1820%29_-_RCIN_405307_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Johann</t>
+          <t>Allan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ZOFFANY</t>
+          <t>RAMSAY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1771-1772</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6231,12 +6196,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>"Les Académiciens de la Royal Academy"</t>
+          <t>"Portrait de George III"</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>"The Academicians of the Royal Academy"</t>
+          <t>"Portrait of George III"</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -6244,19 +6209,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>100,7 cm</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>147,3 cm</t>
-        </is>
-      </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U85" t="n">
@@ -6266,52 +6221,52 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Watsonandtheshark-original.jpg/1280px-Watsonandtheshark-original.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Allan_Ramsay_-_Jean-Jacques_Rousseau_%281712_-_1778%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>John Singleton</t>
+          <t>Allan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>RAMSAY</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Édimbourg</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Scottish National Portrait Gallery</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>"Watson et le requin"</t>
+          <t>"Portrait de Jean-Jacques Rousseau"</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>"Watson and the Shark"</t>
+          <t>"Portrait of Jean-Jacques Rousseau"</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -6321,17 +6276,17 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>182,1 cm</t>
+          <t>75,9 cm</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>229,7 cm</t>
+          <t>62,9 cm</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>américaine</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U86" t="n">
@@ -6341,32 +6296,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/79/Le-discret-by-ducreux.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/30/Master_Hare%2C_par_Joshua_Reynolds.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DUCREUX</t>
+          <t>REYNOLDS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1788-1789</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6381,7 +6336,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>"Le Discret"</t>
+          <t>"Master Hare"</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -6389,9 +6344,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>77,5 cm</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>63,6 cm</t>
+        </is>
+      </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U87" t="n">
@@ -6401,47 +6366,52 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg/960px-Joseph_Ducreux_-_Self-Portrait%2C_Yawning_-_71.PA.56_-_J._Paul_Getty_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Commodore_the_Honourable_Augustus_Keppel_by_Sir_Joshua_Reynolds_1749.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DUCREUX</t>
+          <t>REYNOLDS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>The J. Paul Getty Museum</t>
+          <t>National Maritime Museum</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>"Autoportrait en bâilleur"</t>
+          <t>"Portrait du commodore Keppel"</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>"Portrait of Commodore Keppel"</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -6449,9 +6419,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>239 cm</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>147 cm</t>
+        </is>
+      </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U88" t="n">
@@ -6461,52 +6441,42 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg/960px-Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Hyacinthe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WRIGHT of DERBY</t>
+          <t>RIGAUD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Londres</t>
+          <t>1701-1702</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Château de Versailles</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>"Une expérience sur un oiseau dans une pompe à air"</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>"An Experiment on a Bird in an Air Pump"</t>
+          <t>"Louis XIV, roi de France "</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -6516,17 +6486,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>183 cm</t>
+          <t>277 cm</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>244 cm</t>
+          <t>194 cm</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U89" t="n">
@@ -6536,52 +6506,47 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg/1280px-Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/56/Hubert_Robert_-_Imaginary_View_of_the_Grande_Galerie_in_the_Louvre_in_Ruins_-_WGA19589.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Hubert</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WRIGHT of DERBY</t>
+          <t>ROBERT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1774-1776</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>"Vésuve en éruption vu de Portici"</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>"Vesuvius from Portici"</t>
+          <t>"Le Louvre en ruines"</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -6589,9 +6554,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>114 cm</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>146 cm</t>
+        </is>
+      </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U90" t="n">
@@ -6601,47 +6576,52 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/3/30/Master_Hare%2C_par_Joshua_Reynolds.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/11/Ivan_Orlov_1765_rokotov.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Fiodor</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>REYNOLDS</t>
+          <t>ROKOTOV</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>environ 1735</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1788-1789</t>
+          <t>1762-1763</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Moscou</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Galerie Tretiakov</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>"Master Hare"</t>
+          <t>"Portrait du comte Orlov"</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>"Portret grafa Orlova (Портрет графа Орлова)"</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -6649,19 +6629,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>77,5 cm</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>63,6 cm</t>
-        </is>
-      </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>russe</t>
         </is>
       </c>
       <c r="U91" t="n">
@@ -6671,52 +6641,52 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/c6/Commodore_the_Honourable_Augustus_Keppel_by_Sir_Joshua_Reynolds_1749.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg/960px-La_Dame_au_voile_Alexander_Roslin_Stockholm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REYNOLDS</t>
+          <t>ROSLIN</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>National Maritime Museum</t>
+          <t>Nationalmuseum</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>"Portrait du commodore Keppel"</t>
+          <t>"La Dame au voile"</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>"Portrait of Commodore Keppel"</t>
+          <t>"Damen med slöjan"</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -6726,17 +6696,17 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>239 cm</t>
+          <t>63 cm</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>147 cm</t>
+          <t>52 cm</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>suédoise</t>
         </is>
       </c>
       <c r="U92" t="n">
@@ -6746,27 +6716,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Nature_morte_aux_figues%2C_par_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg/960px-Alexander_Roslin_-_Self-Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MELÉNDEZ</t>
+          <t>ROSLIN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6776,32 +6746,42 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Nationalmuseum</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>"Nature morte aux figues"</t>
+          <t>"Autoportrait"</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>"Bodegón de higos"</t>
+          <t>"Självporträtt"</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>46 cm</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>38 cm</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>suédoise</t>
         </is>
       </c>
       <c r="U93" t="n">
@@ -6811,72 +6791,72 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Self-portrait_Holding_an_Academic_Study_by_Luis_Mel%C3%A9ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg/960px-Gilbert_Stuart%2C_George_Washington_%28Lansdowne_portrait%2C_1796%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MELÉNDEZ</t>
+          <t>STUART</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>National Portrait Gallery</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
+          <t>"Portrait de George Washington (Lansdowne)"</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>"Autorretrato"</t>
+          <t>"George Washington (Lansdowne Portrait)"</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>46 cm</t>
+          <t>247,6 cm</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>38 cm</t>
+          <t>158,7 cm</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>espagnole</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U94" t="n">
@@ -6886,52 +6866,67 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d2/%27Sitting_Tiger%27_by_Maruyama_Okyo%2C_1777%2C_Minneapolis_Institute_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Whistlejacket_by_George_Stubbs.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ōkyo</t>
+          <t>George</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MARUYAMA</t>
+          <t>STUBBS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Minneapolis Institute of Art</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>"Tigre assis"</t>
+          <t>"Whistlejacket"</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Encre et couleurs sur soie</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>292 cm</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>246,4 cm</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>japonaise</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U95" t="n">
@@ -6941,67 +6936,62 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/8/88/Maurice_Quentin_de_La_Tour_-_Marquise_de_Pompadour_-_WGA12359.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/36/George_Stubbs_-_A_Lion_Attacking_a_Horse_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Maurice Quentin</t>
+          <t>George</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>de la TOUR</t>
+          <t>STUBBS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1748-1755</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New Haven</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Yale Center for British Art</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>"Portrait de Madame de Pompadour"</t>
+          <t>"Un lion attaquant un cheval"</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>"A Lion Attacking a Horse"</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Pastel</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>175 cm</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>128 cm</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U96" t="n">
@@ -7011,57 +7001,72 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/2d/Maurice_Quentin_de_La_Tour_-_Portrait_de_Jean_Le_Rond_d%27Alembert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/Giambattista_Tiepolo_-_The_Banquet_of_Cleopatra_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Maurice Quentin</t>
+          <t>Giovanni Battista</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>de la TOUR</t>
+          <t>TIEPOLO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1743-1744</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Melbourne</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>National Gallery of Victoria</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>"Portrait de d'Alembert"</t>
+          <t>"Le Banquet de Cléopâtre"</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>"Il Banchetto di Cleopatra"</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>248,2 cm</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>357 cm</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U97" t="n">
@@ -7071,52 +7076,57 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg/960px-Nicolas_de_Largilli%C3%A8re_-_Portrait_de_Voltaire_%281694-1778%29_en_1718_-_P208_-_mus%C3%A9e_Carnavalet_-_5_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/03/Giovanni_Battista_Tiepolo_-_Apollo_and_the_Continents_-_WGA22323.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Giovanni Battista</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>de LARGILLIÈRE</t>
+          <t>TIEPOLO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1752-1753</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Château de Versailles</t>
+          <t>Résidence de Wurtzbourg</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>"Portrait de Voltaire jeune"</t>
+          <t>"Apollon et les Continents (fresque de l'escalier)"</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>"Apollo e i Continenti"</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Fresque</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U98" t="n">
@@ -7126,52 +7136,47 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/10/Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg/960px-Ca%27_Rezzonico_-_Il_rinoceronte_1751_-_Pietro_Longhi_.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/42/Charles-Andr%C3%A9%2C_dit_Carle_Vanloo_-_Halte_de_chasse_%281737%29.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Carle</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LONGHI</t>
+          <t>van LOO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Ca' Rezzonico</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>"Le Rhinocéros"</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>"Il Rinoceronte"</t>
+          <t>"Halte de chasse"</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -7181,17 +7186,17 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>62 cm</t>
+          <t>216 cm</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>50 cm</t>
+          <t>276 cm</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U99" t="n">
@@ -7201,52 +7206,47 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/5d/Ballando_lesson_by_Pietro_Longhi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/04/Une_sultane_buvant_du_caf%C3%A9_Carle_Van_Loo_ch%C3%A2teau_de_Bellevue.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Carle</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LONGHI</t>
+          <t>van LOO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Saint-Pétersbourg</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Ca' Rezzonico</t>
+          <t>Musée de l'Ermitage</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>"La Leçon de danse"</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>"La Lezione di danza"</t>
+          <t>"La Sultane prenant du café"</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -7254,19 +7254,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>61 cm</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>49 cm</t>
-        </is>
-      </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U100" t="n">
@@ -7276,52 +7266,47 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/28/Pompeo_Girolamo_Batoni_Thomas_William_Coke.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/4/4e/Deuxieme_vue_du_port_de_Bordeaux_prise_du_ch%C3%A2teau_Trompette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pompeo</t>
+          <t>Claude Joseph</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BATONI</t>
+          <t>VERNET</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Holkham Hall</t>
+          <t>Musée national de la Marine</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>"Portrait de Thomas William Coke"</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>"Ritratto di Thomas William Coke"</t>
+          <t>"Vue du port de Bordeaux"</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -7329,9 +7314,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>165 cm</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>263 cm</t>
+        </is>
+      </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U101" t="n">
@@ -7341,52 +7336,47 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/33/Pompeo_Batoni_002.jpg/960px-Pompeo_Batoni_002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg/1280px-Vernet%2C_Claude_Joseph_-_The_Shipwreck_-_1772.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pompeo</t>
+          <t>Claude Joseph</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BATONI</t>
+          <t>VERNET</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Kunsthistorisches Museum</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>"Portrait de Joseph II et Léopold de Toscane"</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>"Ritratto di Giuseppe II e Leopoldo di Toscana"</t>
+          <t>"Un naufrage"</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -7394,19 +7384,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>c.246 cm</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>c.172 cm</t>
-        </is>
-      </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U102" t="n">
@@ -7416,17 +7396,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/66/Richard_Wilson_-_Llyn-y-Cau%2C_Cader_Idris_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg/1280px-Claude-Joseph_Vernet_-_A_Shipwreck_in_Stormy_Seas_%28Temp%C3%AAte%29_-_c_1773_-_National_Gallery_UKFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Claude Joseph</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WILSON</t>
+          <t>VERNET</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7436,12 +7416,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7451,12 +7431,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>"Llyn-y-Cau, Cader Idris"</t>
+          <t>"La Tempête"</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -7464,19 +7444,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>51,1 cm</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>61,9 cm</t>
-        </is>
-      </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U103" t="n">
@@ -7486,52 +7456,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/24/Richard_Wilson_-_Rome_from_the_Villa_Madama_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/35/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Élisabeth</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WILSON</t>
+          <t>VIGÉE LE BRUN</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1782-1783</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>New Haven</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Yale Center for British Art</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>"Rome from the Villa Madama"</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>"Rome from the Villa Madama"</t>
+          <t>"Autoportrait au chapeau de paille"</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -7539,9 +7504,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>97,8 cm</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>70,5 cm</t>
+        </is>
+      </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U104" t="n">
@@ -7551,72 +7526,62 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/c/ca/Rosalba_Carriera_Self-portrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg/960px-Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rosalba</t>
+          <t>Élisabeth</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CARRIERA</t>
+          <t>VIGÉE LE BRUN</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1709</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Florence</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Galerie des Offices</t>
+          <t>Château de Versailles</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>"Autoritratto"</t>
+          <t>"Marie-Antoinette avec une rose"</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>46 cm</t>
+          <t>113 cm</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>38 cm</t>
+          <t>87 cm</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U105" t="n">
@@ -7626,62 +7591,67 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/4/47/Rosalba_Carriera_-_Young_Girl_Holding_a_Monkey_-_WGA04508.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/3/3e/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rosalba</t>
+          <t>Élisabeth</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CARRIERA</t>
+          <t>VIGÉE LE BRUN</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Dresde</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Gemäldegalerie</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>"Portrait de jeune fille au singe"</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>"Ritratto di fanciulla con scimmietta"</t>
+          <t>"Autoportrait avec sa fille Julie"</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Huile sur bois</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>130 cm</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>94 cm</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U106" t="n">
@@ -7691,52 +7661,47 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/52/Thomas_Gainsborough_-_Mr_and_Mrs_Andrews.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg/1280px-L%27Embarquement_pour_Cyth%C3%A8re%2C_by_Antoine_Watteau%2C_from_C2RMF_retouched.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Jean-Antoine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GAINSBOROUGH</t>
+          <t>WATTEAU</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>"Monsieur et Madame Andrews"</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>"Mr and Mrs Andrews"</t>
+          <t>"Le Pèlerinage à l'île de Cythère"</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -7746,72 +7711,67 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>69,8 cm</t>
+          <t>129 cm</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>119,4 cm</t>
+          <t>194 cm</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7e/Thomas_Gainsborough_-_The_Blue_Boy_%28The_Huntington_Library%2C_San_Marino_L._A.%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/Jean-Antoine_Watteau_-_Pierrot%2C_dit_autrefois_GillesFXD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Jean-Antoine</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GAINSBOROUGH</t>
+          <t>WATTEAU</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1718-1719</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Californie</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>The Huntington</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>"Le Garçon bleu"</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>"The Blue Boy"</t>
+          <t>"Pierrot, dit autrefois Gilles"</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -7821,72 +7781,67 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>178 cm</t>
+          <t>184,5 cm</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>122 cm</t>
+          <t>149,5 cm</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/ac/Catherine_II_walking_by_V.Borovikovskiy_%281794%2C_Tretyakov_gallery%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/c7/L%27enseigne_de_Gersaint.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Jean-Antoine</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BOROVIKOVSKY</t>
+          <t>WATTEAU</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Moscou</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Galerie Tretiakov</t>
+          <t>Schloss Charlottenburg</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>"Catherine II en promenade au parc de Tsarskoïe Selo"</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>"Portret Yekateriny II na progulke (Портрет Екатерины II на прогулке)"</t>
+          <t>"L'Enseigne de Gersaint"</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -7894,64 +7849,69 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>166 cm</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>306 cm</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/70/Borovikovsky_pt_gagarinyh.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b8/Jean-Antoine_Watteau_-_L%27indiff%C3%A9rent.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Jean-Antoine</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BOROVIKOVSKY</t>
+          <t>WATTEAU</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Moscou</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Galerie Tretiakov</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>"Portrait des sœurs Gagarine"</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>"Portret sestyor Gagarinykh (Портрет сестёр Гагариных)"</t>
+          <t>"L'Indifférent"</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -7959,139 +7919,144 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>25,5 cm</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>19 cm</t>
+        </is>
+      </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>russe</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ac/Europe_a_Prophecy_copy_K_plate_01.jpg/960px-Europe_a_Prophecy_copy_K_plate_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Jean-Antoine_Watteau_-_Mezzetin.JPG/960px-Jean-Antoine_Watteau_-_Mezzetin.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jean-Antoine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BLAKE</t>
+          <t>WATTEAU</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1718-1720</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>l’Université de Cambridge</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Fitzwilliam Museum</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>"L’Ancien des Jours ou Le Grand Architecte"</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>"The Ancient of Days"</t>
+          <t>"Le Mezzetin"</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gravure à l'eau-forte rehaussée à l'aquarelle et à l'encre</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>23,3 cm</t>
+          <t>55,2 cm</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>16,8 cm</t>
+          <t>43,2 cm</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/William_Hogarth_038.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/The_Death_of_General_Wolfe_B.West%2C1770.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HOGARTH</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>National Gallery of Canada</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>"Le Mariage à la mode (I - Le Contrat de mariage)"</t>
+          <t>"La Mort du général Wolfe"</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>"Marriage A-la-Mode: 1, The Marriage Settlement"</t>
+          <t>"The Death of General Wolfe"</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -8101,72 +8066,72 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>69,9 cm</t>
+          <t>152,6 cm</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>90,8 cm</t>
+          <t>214,5 cm</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/William_Hogarth_006.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Benjamin_West_003.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HOGARTH</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1771-1772</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Philadelphie</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Tate Britain</t>
+          <t>Pennsylvania Academy of the Fine Arts</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>"Le Peintre et son carlin (autoportrait au chien Trump)"</t>
+          <t>"Guillaume Penn et les Indiens"</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>"The Painter and his Pug"</t>
+          <t>"Penn's Treaty with the Indians"</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -8176,52 +8141,52 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>90 cm</t>
+          <t>191,8 cm</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>69,9 cm</t>
+          <t>273,7 cm</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>américaine</t>
         </is>
       </c>
       <c r="U113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/0/03/William_Hogarth_047.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/66/Richard_Wilson_-_Llyn-y-Cau%2C_Cader_Idris_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HOGARTH</t>
+          <t>WILSON</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8231,17 +8196,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>National Gallery</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>"Les Enfants Graham"</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>"The Graham Children"</t>
+          <t>"Llyn-y-Cau, Cader Idris"</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -8251,12 +8211,12 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>162,5 cm</t>
+          <t>51,1 cm</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>181 cm</t>
+          <t>61,9 cm</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -8265,58 +8225,68 @@
         </is>
       </c>
       <c r="U114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/Yuan_Jiang_-_Landscape_with_Summer_Villa_-_62.70.10_-_Minneapolis_Institute_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/24/Richard_Wilson_-_Rome_from_the_Villa_Madama_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>YUAN</t>
+          <t>WILSON</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>environ 1671</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>environ 1746</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>18e siècle</t>
+          <t>1753</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>New Haven</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Minneapolis Institute of Art</t>
+          <t>Yale Center for British Art</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>"Paysage avec villa d'été"</t>
+          <t>"Rome from the Villa Madama"</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>"Rome from the Villa Madama"</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Encre et couleurs sur soie</t>
+          <t>Huile sur toile</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>chinoise</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U115" t="n">
@@ -8326,62 +8296,72 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/59/Zheng_Xie_-_Bamboo_and_Rocks_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg/1280px-An_Experiment_on_a_Bird_in_an_Air_Pump_by_Joseph_Wright_of_Derby%2C_1768.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Xie</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ZHENG</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>BANQIAO</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>BANQIAO</t>
+          <t>WRIGHT of DERBY</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>18e siècle</t>
+          <t>1768</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Minneapolis Institute of Art</t>
+          <t>National Gallery</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>"Bambous et rochers"</t>
+          <t>"Une expérience sur un oiseau dans une pompe à air"</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>"An Experiment on a Bird in an Air Pump"</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Encre sur papier</t>
+          <t>Huile sur toile</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>183 cm</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>244 cm</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>chinoise</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U116" t="n">
@@ -8391,42 +8371,52 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg/960px-Hyacinthe_Rigaud_-_Louis_XIV%2C_roi_de_France_%281638-1715%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg/1280px-Joseph_Wright_of_Derby_-_Vesuvius_from_Portici.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Hyacinthe</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RIGAUD</t>
+          <t>WRIGHT of DERBY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1701-1702</t>
+          <t>1774-1776</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Château de Versailles</t>
+          <t>Tate Britain</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>"Louis XIV, roi de France "</t>
+          <t>"Vésuve en éruption vu de Portici"</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>"Vesuvius from Portici"</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -8434,19 +8424,9 @@
           <t>Huile sur toile</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>277 cm</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>194 cm</t>
-        </is>
-      </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>anglaise (Royaume-Uni)</t>
         </is>
       </c>
       <c r="U117" t="n">
@@ -8456,62 +8436,52 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/%27The_Tame_Magpie%27%2C_oil_on_canvas_painting_by_Alessandro_Magnasco%2C_c._1707-8%2C_Metropolitan_Museum_of_Art.JPG/1280px-%27The_Tame_Magpie%27%2C_oil_on_canvas_painting_by_Alessandro_Magnasco%2C_c._1707-8%2C_Metropolitan_Museum_of_Art.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/Yuan_Jiang_-_Landscape_with_Summer_Villa_-_62.70.10_-_Minneapolis_Institute_of_Art.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Alessandro</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MAGNASCO</t>
+          <t>YUAN</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>environ 1671</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>environ 1746</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1707-1708</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>New York</t>
+          <t>18e siècle</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Minneapolis Institute of Art</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>"La Pie apprivoisée"</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>"La Gazza ammaestrata"</t>
+          <t>"Paysage avec villa d'été"</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Encre et couleurs sur soie</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>chinoise</t>
         </is>
       </c>
       <c r="U118" t="n">
@@ -8521,52 +8491,62 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/D%C3%A9jeuner_de_jambon_-_Nicolas_Lancret_-_mus%C3%A9e_Cond%C3%A9.jpg/960px-D%C3%A9jeuner_de_jambon_-_Nicolas_Lancret_-_mus%C3%A9e_Cond%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/5/59/Zheng_Xie_-_Bamboo_and_Rocks_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LANCRET</t>
+          <t>ZHENG</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BANQIAO</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>BANQIAO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>18e siècle</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Château de Chantilly</t>
+          <t>Minneapolis Institute of Art</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>"Le Déjeuner de jambon"</t>
+          <t>"Bambous et rochers"</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Huile sur toile</t>
+          <t>Encre sur papier</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>chinoise</t>
         </is>
       </c>
       <c r="U119" t="n">
@@ -8576,42 +8556,52 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/9/95/Natoire_-_Psych%C3%A9_%C3%A0_sa_toilette.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg/1280px-Johan_Zoffany_-_Tribuna_of_the_Uffizi_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Charles-Joseph</t>
+          <t>Johann</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NATOIRE</t>
+          <t>ZOFFANY</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1772-1778</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Musée d’Art de La Nouvelle-Orléans</t>
+          <t>Royal Collection</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>"Psyché à sa toilette"</t>
+          <t>"La Tribune des Offices"</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>"The Tribuna of the Uffizi"</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -8619,9 +8609,19 @@
           <t>Huile sur toile</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>123,5 cm</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>155 cm</t>
+        </is>
+      </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U120" t="n">
@@ -8631,52 +8631,52 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Portrait_of_Elizabeth_Farren%2C_by_Thomas_Lawrence.jpg/960px-Portrait_of_Elizabeth_Farren%2C_by_Thomas_Lawrence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/c/ca/The_Portraits_of_the_Academicians_of_the_Royal_Academy%2C_1771-72%2C_oil_on_canvas%2C_The_Royal_Collection_by_Johan_Zoffany.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Johann</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LAWRENCE</t>
+          <t>ZOFFANY</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1771-1772</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Royal Collection</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>"Portrait d’Elizabeth Farren "</t>
+          <t>"Les Académiciens de la Royal Academy"</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>"Portrait of Elizabeth Farren"</t>
+          <t>"The Academicians of the Royal Academy"</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -8686,17 +8686,17 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>238,8 cm</t>
+          <t>100,7 cm</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>146,7 cm</t>
+          <t>147,3 cm</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>anglaise (Royaume-Uni)</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U121" t="n">

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -4291,7 +4291,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Freer Gallery of Art (National Museum of Asian Art)</t>
+          <t>Freer Gallery of Art</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">

--- a/quizzes/peinture-18e.xlsx
+++ b/quizzes/peinture-18e.xlsx
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>environ 1735</t>
+          <t>1735 environ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>environ 1671</t>
+          <t>1671 environ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>environ 1746</t>
+          <t>1746 environ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
